--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/shap_summary.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/shap_summary.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.04828259122900901</v>
+        <v>0.03809923856570584</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04184414359790391</v>
+        <v>0.02986247841968954</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -514,11 +514,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03108755445157096</v>
+        <v>0.02822370535110387</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -537,11 +537,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02984305336398419</v>
+        <v>0.02783210413185772</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -560,11 +560,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02969795660084256</v>
+        <v>0.02477820246387299</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.02293194740646718</v>
+        <v>0.02346899644980449</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -606,11 +606,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01627506532326452</v>
+        <v>0.0180562061614221</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -629,11 +629,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01217644399684354</v>
+        <v>0.01142612054834156</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04615599483440821</v>
+        <v>0.02755243525333835</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.03547597371511854</v>
+        <v>0.02614886364854875</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03212477816007105</v>
+        <v>0.02493846045756679</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0272919409543162</v>
+        <v>0.02465763669349604</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -744,11 +744,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02716607315208846</v>
+        <v>0.0232061510896285</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
@@ -767,11 +767,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.02482034492766926</v>
+        <v>0.01872546511130856</v>
       </c>
       <c r="E15" t="n">
         <v>6</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.02237369912313392</v>
+        <v>0.01648148667149018</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
@@ -813,11 +813,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.008768711967088257</v>
+        <v>0.0101841140624342</v>
       </c>
       <c r="E17" t="n">
         <v>8</v>
@@ -836,11 +836,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.0297348840435253</v>
+        <v>0.03011478526552338</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -859,11 +859,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02355123688879636</v>
+        <v>0.02379375985688522</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -882,11 +882,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.02005168858255094</v>
+        <v>0.02196672584157765</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -905,11 +905,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.01781121735390541</v>
+        <v>0.02100621269373126</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -928,11 +928,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.01734146441700337</v>
+        <v>0.01796748436583282</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
@@ -951,11 +951,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.01703824801880433</v>
+        <v>0.01723538430882434</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
@@ -974,11 +974,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.01666695536583618</v>
+        <v>0.01513508435337485</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
@@ -997,11 +997,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.01341302701381351</v>
+        <v>0.01081352773931926</v>
       </c>
       <c r="E25" t="n">
         <v>8</v>
@@ -1020,11 +1020,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.02736537406851321</v>
+        <v>0.02052478693461994</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.01967761615879031</v>
+        <v>0.02052389732690537</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -1066,11 +1066,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0190504795020635</v>
+        <v>0.01984637049637663</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1089,11 +1089,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.01566856155392221</v>
+        <v>0.01773297533894026</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.01550413159022807</v>
+        <v>0.01369351529399288</v>
       </c>
       <c r="E30" t="n">
         <v>5</v>
@@ -1135,11 +1135,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.01494304937322417</v>
+        <v>0.01262156412458175</v>
       </c>
       <c r="E31" t="n">
         <v>6</v>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.01330364497665305</v>
+        <v>0.01193060714246621</v>
       </c>
       <c r="E32" t="n">
         <v>7</v>
@@ -1181,11 +1181,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.006523108888143994</v>
+        <v>0.009252724827581034</v>
       </c>
       <c r="E33" t="n">
         <v>8</v>
@@ -1204,11 +1204,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.04828990137877086</v>
+        <v>0.03562855577852648</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.03182243971761925</v>
+        <v>0.02951102027823595</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.02716267535028884</v>
+        <v>0.02563708471063694</v>
       </c>
       <c r="E36" t="n">
         <v>3</v>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.02648679697384979</v>
+        <v>0.02485814475021752</v>
       </c>
       <c r="E37" t="n">
         <v>4</v>
@@ -1296,11 +1296,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.02535413850539384</v>
+        <v>0.02340718697741714</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
@@ -1319,11 +1319,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.02531524645874483</v>
+        <v>0.02086724378575412</v>
       </c>
       <c r="E39" t="n">
         <v>6</v>
@@ -1342,11 +1342,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.02154729521268057</v>
+        <v>0.01772731202062739</v>
       </c>
       <c r="E40" t="n">
         <v>7</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.006268568922081305</v>
+        <v>0.009257857531702482</v>
       </c>
       <c r="E41" t="n">
         <v>8</v>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.03388854266615276</v>
+        <v>0.0382447927828469</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.03000760196981985</v>
+        <v>0.03226840869993491</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.02614395060195533</v>
+        <v>0.03052751415352695</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.02431095641227147</v>
+        <v>0.02699551404953445</v>
       </c>
       <c r="E45" t="n">
         <v>4</v>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.02129721551220428</v>
+        <v>0.02138438892556659</v>
       </c>
       <c r="E46" t="n">
         <v>5</v>
@@ -1503,11 +1503,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.01914797364519371</v>
+        <v>0.0206448969524422</v>
       </c>
       <c r="E47" t="n">
         <v>6</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.01709253137797812</v>
+        <v>0.01949594772039145</v>
       </c>
       <c r="E48" t="n">
         <v>7</v>
@@ -1549,11 +1549,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.01085626325320279</v>
+        <v>0.003969506059886799</v>
       </c>
       <c r="E49" t="n">
         <v>8</v>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.02504461504999842</v>
+        <v>0.02293622100741881</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.02444673338520769</v>
+        <v>0.02292714912459093</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
@@ -1618,11 +1618,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.02188321190003912</v>
+        <v>0.02200441769333783</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.02068899123389273</v>
+        <v>0.02197684191246888</v>
       </c>
       <c r="E53" t="n">
         <v>4</v>
@@ -1664,11 +1664,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.01963715339941029</v>
+        <v>0.02161246803635694</v>
       </c>
       <c r="E54" t="n">
         <v>5</v>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.01948576595817277</v>
+        <v>0.01922440061891202</v>
       </c>
       <c r="E55" t="n">
         <v>6</v>
@@ -1710,11 +1710,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.01863366557680992</v>
+        <v>0.0192097159009717</v>
       </c>
       <c r="E56" t="n">
         <v>7</v>
@@ -1733,11 +1733,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.01402453668471652</v>
+        <v>0.008722585109615655</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -1756,11 +1756,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.04078750777312464</v>
+        <v>0.03436380317597383</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.04045492188626103</v>
+        <v>0.03112286152985997</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -1802,11 +1802,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.03057650082350526</v>
+        <v>0.02823769550895757</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.02380220073023713</v>
+        <v>0.02788510034100031</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.02186656610881326</v>
+        <v>0.01960850816197564</v>
       </c>
       <c r="E62" t="n">
         <v>5</v>
@@ -1871,11 +1871,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.01914053818007209</v>
+        <v>0.0182276949788352</v>
       </c>
       <c r="E63" t="n">
         <v>6</v>
@@ -1894,11 +1894,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0190737813193981</v>
+        <v>0.01694520235437454</v>
       </c>
       <c r="E64" t="n">
         <v>7</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.006963083734684938</v>
+        <v>0.009826923791740029</v>
       </c>
       <c r="E65" t="n">
         <v>8</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.04055553676141661</v>
+        <v>0.04434580723534823</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.03621655660211949</v>
+        <v>0.03453647680129834</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.03109035902193429</v>
+        <v>0.03092061396898714</v>
       </c>
       <c r="E68" t="n">
         <v>3</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.02965019308543819</v>
+        <v>0.03005910564536191</v>
       </c>
       <c r="E69" t="n">
         <v>4</v>
@@ -2032,11 +2032,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.02850822812895914</v>
+        <v>0.02903082285928507</v>
       </c>
       <c r="E70" t="n">
         <v>5</v>
@@ -2055,11 +2055,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.02848394982623727</v>
+        <v>0.02688129924940866</v>
       </c>
       <c r="E71" t="n">
         <v>6</v>
@@ -2078,11 +2078,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.02234420175426229</v>
+        <v>0.02396111097398267</v>
       </c>
       <c r="E72" t="n">
         <v>7</v>
@@ -2101,11 +2101,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.009736225587284205</v>
+        <v>0.02017674001475402</v>
       </c>
       <c r="E73" t="n">
         <v>8</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.03152006716729635</v>
+        <v>0.03758177776032348</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0252187189106044</v>
+        <v>0.03048525221415673</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.02296109888829858</v>
+        <v>0.02579936926840425</v>
       </c>
       <c r="E76" t="n">
         <v>3</v>
@@ -2193,11 +2193,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.02172705534313994</v>
+        <v>0.0252647860755448</v>
       </c>
       <c r="E77" t="n">
         <v>4</v>
@@ -2216,11 +2216,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.02127104354085474</v>
+        <v>0.02040245184024701</v>
       </c>
       <c r="E78" t="n">
         <v>5</v>
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.01990634682860696</v>
+        <v>0.01883890088819499</v>
       </c>
       <c r="E79" t="n">
         <v>6</v>
@@ -2262,11 +2262,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.01841114780940585</v>
+        <v>0.01834722829844156</v>
       </c>
       <c r="E80" t="n">
         <v>7</v>
@@ -2285,11 +2285,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.01513950313502251</v>
+        <v>0.01770103078920696</v>
       </c>
       <c r="E81" t="n">
         <v>8</v>
@@ -2308,11 +2308,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.03197838174348877</v>
+        <v>0.03563454222560034</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.03089554966070407</v>
+        <v>0.03397153100125615</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
@@ -2354,11 +2354,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.03038346386832865</v>
+        <v>0.03196870136715607</v>
       </c>
       <c r="E84" t="n">
         <v>3</v>
@@ -2377,11 +2377,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.03026795649914238</v>
+        <v>0.02954363547470555</v>
       </c>
       <c r="E85" t="n">
         <v>4</v>
@@ -2400,11 +2400,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.02912005451492548</v>
+        <v>0.02642060811945672</v>
       </c>
       <c r="E86" t="n">
         <v>5</v>
@@ -2423,11 +2423,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.02390008969841705</v>
+        <v>0.02640917102097656</v>
       </c>
       <c r="E87" t="n">
         <v>6</v>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.02108286778746843</v>
+        <v>0.02128404471082854</v>
       </c>
       <c r="E88" t="n">
         <v>7</v>
@@ -2469,11 +2469,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.008760435335948513</v>
+        <v>0.007726228032952785</v>
       </c>
       <c r="E89" t="n">
         <v>8</v>
@@ -2492,11 +2492,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.03097613547193547</v>
+        <v>0.03128778135807331</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.03034133948211119</v>
+        <v>0.02917337198263555</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -2538,11 +2538,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.02470617223879241</v>
+        <v>0.02879210076533224</v>
       </c>
       <c r="E92" t="n">
         <v>3</v>
@@ -2561,11 +2561,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.01827843290295631</v>
+        <v>0.02332753794932088</v>
       </c>
       <c r="E93" t="n">
         <v>4</v>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.01816739419491548</v>
+        <v>0.02229932352046545</v>
       </c>
       <c r="E94" t="n">
         <v>5</v>
@@ -2607,11 +2607,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.01509312660904848</v>
+        <v>0.01597668057432541</v>
       </c>
       <c r="E95" t="n">
         <v>6</v>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.01278746970472304</v>
+        <v>0.01586492740322685</v>
       </c>
       <c r="E96" t="n">
         <v>7</v>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.00414089399437291</v>
+        <v>0.005928705010777849</v>
       </c>
       <c r="E97" t="n">
         <v>8</v>
@@ -2676,11 +2676,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.02330734089617804</v>
+        <v>0.01998120909333736</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -2699,11 +2699,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.02052170396166321</v>
+        <v>0.01820324115920274</v>
       </c>
       <c r="E99" t="n">
         <v>2</v>
@@ -2722,11 +2722,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.01956939096004446</v>
+        <v>0.01808787809935173</v>
       </c>
       <c r="E100" t="n">
         <v>3</v>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.01551275264966242</v>
+        <v>0.01795721740526312</v>
       </c>
       <c r="E101" t="n">
         <v>4</v>
@@ -2768,11 +2768,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.0148210379711705</v>
+        <v>0.01737500994598168</v>
       </c>
       <c r="E102" t="n">
         <v>5</v>
@@ -2791,11 +2791,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.0144739648620444</v>
+        <v>0.01691778258110319</v>
       </c>
       <c r="E103" t="n">
         <v>6</v>
@@ -2814,11 +2814,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.01266310588951535</v>
+        <v>0.01252108379921612</v>
       </c>
       <c r="E104" t="n">
         <v>7</v>
@@ -2837,11 +2837,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.005338298123443328</v>
+        <v>0.007633528650457241</v>
       </c>
       <c r="E105" t="n">
         <v>8</v>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.0409993870133311</v>
+        <v>0.03490515958752668</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.0342621290014124</v>
+        <v>0.03428678230095244</v>
       </c>
       <c r="E107" t="n">
         <v>2</v>
@@ -2906,11 +2906,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.03382112941700471</v>
+        <v>0.03243357366139141</v>
       </c>
       <c r="E108" t="n">
         <v>3</v>
@@ -2929,11 +2929,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.03140102841850707</v>
+        <v>0.02845507147259195</v>
       </c>
       <c r="E109" t="n">
         <v>4</v>
@@ -2952,11 +2952,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.0243310617619357</v>
+        <v>0.02618550447696637</v>
       </c>
       <c r="E110" t="n">
         <v>5</v>
@@ -2975,11 +2975,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.02317626009024564</v>
+        <v>0.02503350053743027</v>
       </c>
       <c r="E111" t="n">
         <v>6</v>
@@ -2998,11 +2998,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.02248695445215057</v>
+        <v>0.01767497174753234</v>
       </c>
       <c r="E112" t="n">
         <v>7</v>
@@ -3021,11 +3021,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.007031815256937367</v>
+        <v>0.009586634041966509</v>
       </c>
       <c r="E113" t="n">
         <v>8</v>
@@ -3044,11 +3044,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.02560316819262314</v>
+        <v>0.02811945678219669</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3067,11 +3067,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.02484793356196494</v>
+        <v>0.02759059688674744</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
@@ -3090,11 +3090,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.02225510487638811</v>
+        <v>0.02438650478155708</v>
       </c>
       <c r="E116" t="n">
         <v>3</v>
@@ -3113,11 +3113,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.02112919898158144</v>
+        <v>0.01872041587415766</v>
       </c>
       <c r="E117" t="n">
         <v>4</v>
@@ -3136,11 +3136,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.01793056761307004</v>
+        <v>0.01863655523051919</v>
       </c>
       <c r="E118" t="n">
         <v>5</v>
@@ -3159,11 +3159,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.01770293336322371</v>
+        <v>0.01817965614842489</v>
       </c>
       <c r="E119" t="n">
         <v>6</v>
@@ -3182,11 +3182,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.0167954901846547</v>
+        <v>0.01771573893868158</v>
       </c>
       <c r="E120" t="n">
         <v>7</v>
@@ -3205,11 +3205,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.007794488620839526</v>
+        <v>0.008788271548505719</v>
       </c>
       <c r="E121" t="n">
         <v>8</v>
@@ -3228,11 +3228,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.03661318172966233</v>
+        <v>0.03341680169935241</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.03597677364216489</v>
+        <v>0.03259244434543936</v>
       </c>
       <c r="E123" t="n">
         <v>2</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.03384277354290513</v>
+        <v>0.03058073938678412</v>
       </c>
       <c r="E124" t="n">
         <v>3</v>
@@ -3297,11 +3297,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.0299680120357606</v>
+        <v>0.02457938142241664</v>
       </c>
       <c r="E125" t="n">
         <v>4</v>
@@ -3320,11 +3320,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.0278145040082474</v>
+        <v>0.02153791118022752</v>
       </c>
       <c r="E126" t="n">
         <v>5</v>
@@ -3343,11 +3343,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.01859049074226465</v>
+        <v>0.01923778916087692</v>
       </c>
       <c r="E127" t="n">
         <v>6</v>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.01713144618248252</v>
+        <v>0.01866928383814323</v>
       </c>
       <c r="E128" t="n">
         <v>7</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.006992250184892006</v>
+        <v>0.008586137756505591</v>
       </c>
       <c r="E129" t="n">
         <v>8</v>
@@ -3412,11 +3412,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.03501225697927684</v>
+        <v>0.03963501720258204</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -3435,11 +3435,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.03178054490038432</v>
+        <v>0.03886398209675424</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.02815254793325148</v>
+        <v>0.03350823717393161</v>
       </c>
       <c r="E132" t="n">
         <v>3</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.02621331103371532</v>
+        <v>0.03285770101026371</v>
       </c>
       <c r="E133" t="n">
         <v>4</v>
@@ -3504,11 +3504,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.02489657902976259</v>
+        <v>0.02313055063524238</v>
       </c>
       <c r="E134" t="n">
         <v>5</v>
@@ -3527,11 +3527,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.02417778824467964</v>
+        <v>0.02077447918051711</v>
       </c>
       <c r="E135" t="n">
         <v>6</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.02363429692527045</v>
+        <v>0.02051745197292682</v>
       </c>
       <c r="E136" t="n">
         <v>7</v>
@@ -3573,11 +3573,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.01757365672623305</v>
+        <v>0.006774872998062511</v>
       </c>
       <c r="E137" t="n">
         <v>8</v>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.04497102499333076</v>
+        <v>0.03764689293797543</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.03383673341853129</v>
+        <v>0.03080508601345025</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -3642,11 +3642,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.02986004426828138</v>
+        <v>0.02732620689380574</v>
       </c>
       <c r="E140" t="n">
         <v>3</v>
@@ -3665,11 +3665,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.02280592342811107</v>
+        <v>0.02145031143010462</v>
       </c>
       <c r="E141" t="n">
         <v>4</v>
@@ -3688,11 +3688,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.01778885905723843</v>
+        <v>0.01571740750211654</v>
       </c>
       <c r="E142" t="n">
         <v>5</v>
@@ -3711,11 +3711,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.01656077432367185</v>
+        <v>0.01561241095620126</v>
       </c>
       <c r="E143" t="n">
         <v>6</v>
@@ -3734,11 +3734,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.01305683014223649</v>
+        <v>0.01542010155059363</v>
       </c>
       <c r="E144" t="n">
         <v>7</v>
@@ -3757,11 +3757,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.00792463776556984</v>
+        <v>0.005385398318680759</v>
       </c>
       <c r="E145" t="n">
         <v>8</v>
@@ -3780,11 +3780,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.03521455900801927</v>
+        <v>0.03582976720680696</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -3803,11 +3803,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.03356590427851604</v>
+        <v>0.02925983997105691</v>
       </c>
       <c r="E147" t="n">
         <v>2</v>
@@ -3826,11 +3826,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.03304048980274495</v>
+        <v>0.02501629498795213</v>
       </c>
       <c r="E148" t="n">
         <v>3</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.02419460832291444</v>
+        <v>0.0245227203527018</v>
       </c>
       <c r="E149" t="n">
         <v>4</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.02409913483300351</v>
+        <v>0.02210638390865794</v>
       </c>
       <c r="E150" t="n">
         <v>5</v>
@@ -3895,11 +3895,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.02225419051635835</v>
+        <v>0.02143815726496291</v>
       </c>
       <c r="E151" t="n">
         <v>6</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.02152376672970915</v>
+        <v>0.01571149468243128</v>
       </c>
       <c r="E152" t="n">
         <v>7</v>
@@ -3941,11 +3941,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.01747843198121671</v>
+        <v>0.01402909862565528</v>
       </c>
       <c r="E153" t="n">
         <v>8</v>
@@ -3964,11 +3964,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.04953568965636855</v>
+        <v>0.03669277804637983</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
@@ -3987,11 +3987,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.03536699036238426</v>
+        <v>0.02965577626102949</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -4010,11 +4010,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.02536680367412777</v>
+        <v>0.02622043534669354</v>
       </c>
       <c r="E156" t="n">
         <v>3</v>
@@ -4033,11 +4033,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.02415871190936637</v>
+        <v>0.02603229594324416</v>
       </c>
       <c r="E157" t="n">
         <v>4</v>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.02242782363739421</v>
+        <v>0.02486153346292808</v>
       </c>
       <c r="E158" t="n">
         <v>5</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.01870803505344009</v>
+        <v>0.02463922761736489</v>
       </c>
       <c r="E159" t="n">
         <v>6</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.01593724931963113</v>
+        <v>0.02057488490421245</v>
       </c>
       <c r="E160" t="n">
         <v>7</v>
@@ -4125,11 +4125,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.01236879212223166</v>
+        <v>0.00492132318598343</v>
       </c>
       <c r="E161" t="n">
         <v>8</v>
@@ -4148,11 +4148,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.0363836631085862</v>
+        <v>0.03110389560142154</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
@@ -4171,11 +4171,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.03296169788546498</v>
+        <v>0.03089131164190282</v>
       </c>
       <c r="E163" t="n">
         <v>2</v>
@@ -4194,11 +4194,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.02462066785403161</v>
+        <v>0.0302289902893275</v>
       </c>
       <c r="E164" t="n">
         <v>3</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.02160650868327472</v>
+        <v>0.02984585686512429</v>
       </c>
       <c r="E165" t="n">
         <v>4</v>
@@ -4240,11 +4240,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.02157388106402518</v>
+        <v>0.02665917115595168</v>
       </c>
       <c r="E166" t="n">
         <v>5</v>
@@ -4263,11 +4263,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.02136455249262553</v>
+        <v>0.02495136823827249</v>
       </c>
       <c r="E167" t="n">
         <v>6</v>
@@ -4286,11 +4286,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.02050235281907425</v>
+        <v>0.0216299176177461</v>
       </c>
       <c r="E168" t="n">
         <v>7</v>
@@ -4309,11 +4309,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.01050485027529579</v>
+        <v>0.01012998702179705</v>
       </c>
       <c r="E169" t="n">
         <v>8</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.02815128451829332</v>
+        <v>0.02885014099936915</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
@@ -4355,11 +4355,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.02457909520316299</v>
+        <v>0.02603822860787072</v>
       </c>
       <c r="E171" t="n">
         <v>2</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.02423407411218686</v>
+        <v>0.02587522171466907</v>
       </c>
       <c r="E172" t="n">
         <v>3</v>
@@ -4401,11 +4401,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.02255420062440627</v>
+        <v>0.02533502720984854</v>
       </c>
       <c r="E173" t="n">
         <v>4</v>
@@ -4424,11 +4424,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.02215251753961981</v>
+        <v>0.02406997864038043</v>
       </c>
       <c r="E174" t="n">
         <v>5</v>
@@ -4447,11 +4447,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.02122106602224478</v>
+        <v>0.02316387917193204</v>
       </c>
       <c r="E175" t="n">
         <v>6</v>
@@ -4470,11 +4470,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.02110891507948457</v>
+        <v>0.01929491973935786</v>
       </c>
       <c r="E176" t="n">
         <v>7</v>
@@ -4493,11 +4493,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.01419900389463982</v>
+        <v>0.009425733531996277</v>
       </c>
       <c r="E177" t="n">
         <v>8</v>
@@ -4516,11 +4516,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.04011943385433388</v>
+        <v>0.03622596838859769</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -4539,11 +4539,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.03506929485386261</v>
+        <v>0.03309907933187912</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -4562,11 +4562,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.02878280590706398</v>
+        <v>0.02596817545888567</v>
       </c>
       <c r="E180" t="n">
         <v>3</v>
@@ -4585,11 +4585,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.0259937963871568</v>
+        <v>0.02544630479066382</v>
       </c>
       <c r="E181" t="n">
         <v>4</v>
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.02344054966607413</v>
+        <v>0.02039460389443083</v>
       </c>
       <c r="E182" t="n">
         <v>5</v>
@@ -4631,11 +4631,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.02211034643201304</v>
+        <v>0.01967640962062391</v>
       </c>
       <c r="E183" t="n">
         <v>6</v>
@@ -4654,11 +4654,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.02132601840144351</v>
+        <v>0.0189380890429362</v>
       </c>
       <c r="E184" t="n">
         <v>7</v>
@@ -4677,11 +4677,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.00700526306994439</v>
+        <v>0.008225438420027879</v>
       </c>
       <c r="E185" t="n">
         <v>8</v>
@@ -4700,11 +4700,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.04672734454016356</v>
+        <v>0.04976062206013869</v>
       </c>
       <c r="E186" t="n">
         <v>1</v>
@@ -4723,11 +4723,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.0424740010189062</v>
+        <v>0.02930970114952488</v>
       </c>
       <c r="E187" t="n">
         <v>2</v>
@@ -4746,11 +4746,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.02770296051320692</v>
+        <v>0.0268792743482487</v>
       </c>
       <c r="E188" t="n">
         <v>3</v>
@@ -4769,11 +4769,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.02564452065722123</v>
+        <v>0.02620366783233376</v>
       </c>
       <c r="E189" t="n">
         <v>4</v>
@@ -4792,11 +4792,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.02337393703158337</v>
+        <v>0.02344029771180048</v>
       </c>
       <c r="E190" t="n">
         <v>5</v>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.02143593367514662</v>
+        <v>0.02100161367065144</v>
       </c>
       <c r="E191" t="n">
         <v>6</v>
@@ -4838,11 +4838,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.02017346833317038</v>
+        <v>0.01904254736978724</v>
       </c>
       <c r="E192" t="n">
         <v>7</v>
@@ -4861,11 +4861,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.01003887334798304</v>
+        <v>0.0138633879841947</v>
       </c>
       <c r="E193" t="n">
         <v>8</v>
@@ -4884,11 +4884,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.03601509161981057</v>
+        <v>0.04210615145277036</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
@@ -4907,11 +4907,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.03564228360118042</v>
+        <v>0.03997636600864762</v>
       </c>
       <c r="E195" t="n">
         <v>2</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.02969588994702118</v>
+        <v>0.03829292570353024</v>
       </c>
       <c r="E196" t="n">
         <v>3</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.02698376003653251</v>
+        <v>0.02470225134075655</v>
       </c>
       <c r="E197" t="n">
         <v>4</v>
@@ -4976,11 +4976,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.02379663616325074</v>
+        <v>0.02265548092510834</v>
       </c>
       <c r="E198" t="n">
         <v>5</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.02074177957487449</v>
+        <v>0.02251733828599085</v>
       </c>
       <c r="E199" t="n">
         <v>6</v>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.01951673790855378</v>
+        <v>0.02134398696191437</v>
       </c>
       <c r="E200" t="n">
         <v>7</v>
@@ -5045,11 +5045,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.01441331029088544</v>
+        <v>0.01595887002208128</v>
       </c>
       <c r="E201" t="n">
         <v>8</v>
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.02853896711768724</v>
+        <v>0.03492245695292501</v>
       </c>
       <c r="E202" t="n">
         <v>1</v>
@@ -5091,11 +5091,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.0277256704822377</v>
+        <v>0.03103900563356133</v>
       </c>
       <c r="E203" t="n">
         <v>2</v>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.02350840205330111</v>
+        <v>0.02622004936051918</v>
       </c>
       <c r="E204" t="n">
         <v>3</v>
@@ -5137,11 +5137,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.01875711928841122</v>
+        <v>0.0214722526990893</v>
       </c>
       <c r="E205" t="n">
         <v>4</v>
@@ -5160,11 +5160,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.01592076400888103</v>
+        <v>0.01999363590897394</v>
       </c>
       <c r="E206" t="n">
         <v>5</v>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.01520528067898069</v>
+        <v>0.01871983617041093</v>
       </c>
       <c r="E207" t="n">
         <v>6</v>
@@ -5206,11 +5206,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.01228949094083414</v>
+        <v>0.01517911205963187</v>
       </c>
       <c r="E208" t="n">
         <v>7</v>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.01200297203488616</v>
+        <v>0.007295815573496175</v>
       </c>
       <c r="E209" t="n">
         <v>8</v>
@@ -5252,11 +5252,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.03666279100423075</v>
+        <v>0.03597010550148029</v>
       </c>
       <c r="E210" t="n">
         <v>1</v>
@@ -5275,11 +5275,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.03048522645991747</v>
+        <v>0.03507848175644375</v>
       </c>
       <c r="E211" t="n">
         <v>2</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.02994050138110418</v>
+        <v>0.03400633721984202</v>
       </c>
       <c r="E212" t="n">
         <v>3</v>
@@ -5321,11 +5321,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.02649180730587564</v>
+        <v>0.03167765842634317</v>
       </c>
       <c r="E213" t="n">
         <v>4</v>
@@ -5344,11 +5344,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.02329110045505703</v>
+        <v>0.02297292753902191</v>
       </c>
       <c r="E214" t="n">
         <v>5</v>
@@ -5367,11 +5367,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.02220559535831964</v>
+        <v>0.01871264748812292</v>
       </c>
       <c r="E215" t="n">
         <v>6</v>
@@ -5390,11 +5390,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.02183048601388665</v>
+        <v>0.01814760869222826</v>
       </c>
       <c r="E216" t="n">
         <v>7</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.01083947111632174</v>
+        <v>0.00482467824898274</v>
       </c>
       <c r="E217" t="n">
         <v>8</v>
@@ -5436,11 +5436,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0.03547752808433706</v>
+        <v>0.03338474742164872</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
@@ -5459,11 +5459,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.03089073291732538</v>
+        <v>0.03280999071711885</v>
       </c>
       <c r="E219" t="n">
         <v>2</v>
@@ -5482,11 +5482,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.02770677589405392</v>
+        <v>0.03161898580265272</v>
       </c>
       <c r="E220" t="n">
         <v>3</v>
@@ -5505,11 +5505,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0.02598598783004517</v>
+        <v>0.02814284356608111</v>
       </c>
       <c r="E221" t="n">
         <v>4</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.02536598485848606</v>
+        <v>0.02753253139352467</v>
       </c>
       <c r="E222" t="n">
         <v>5</v>
@@ -5551,11 +5551,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.02370857810642591</v>
+        <v>0.02410207397645309</v>
       </c>
       <c r="E223" t="n">
         <v>6</v>
@@ -5574,11 +5574,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.0224487808369249</v>
+        <v>0.02061013049871417</v>
       </c>
       <c r="E224" t="n">
         <v>7</v>
@@ -5597,11 +5597,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.02060581932349284</v>
+        <v>0.02036163463200307</v>
       </c>
       <c r="E225" t="n">
         <v>8</v>
@@ -5620,11 +5620,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.04135348618317817</v>
+        <v>0.03890354667296107</v>
       </c>
       <c r="E226" t="n">
         <v>1</v>
@@ -5643,11 +5643,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.02564885862728471</v>
+        <v>0.03886290912760366</v>
       </c>
       <c r="E227" t="n">
         <v>2</v>
@@ -5666,11 +5666,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.02146005803593381</v>
+        <v>0.0291242057122738</v>
       </c>
       <c r="E228" t="n">
         <v>3</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.02142031340124109</v>
+        <v>0.02672979931381477</v>
       </c>
       <c r="E229" t="n">
         <v>4</v>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0.02133120622507554</v>
+        <v>0.02347119922458026</v>
       </c>
       <c r="E230" t="n">
         <v>5</v>
@@ -5735,11 +5735,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.01906850582238503</v>
+        <v>0.02305382330236285</v>
       </c>
       <c r="E231" t="n">
         <v>6</v>
@@ -5758,11 +5758,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.01579937772687545</v>
+        <v>0.02271935926981739</v>
       </c>
       <c r="E232" t="n">
         <v>7</v>
@@ -5781,11 +5781,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0.005568768753822653</v>
+        <v>0.01134574281151608</v>
       </c>
       <c r="E233" t="n">
         <v>8</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.02946579695653979</v>
+        <v>0.03077182763434903</v>
       </c>
       <c r="E234" t="n">
         <v>1</v>
@@ -5827,11 +5827,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.02892684647248283</v>
+        <v>0.02255045184471511</v>
       </c>
       <c r="E235" t="n">
         <v>2</v>
@@ -5850,11 +5850,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.02629319576363154</v>
+        <v>0.02026973262516607</v>
       </c>
       <c r="E236" t="n">
         <v>3</v>
@@ -5873,11 +5873,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.02617012944126198</v>
+        <v>0.01985642500955628</v>
       </c>
       <c r="E237" t="n">
         <v>4</v>
@@ -5896,11 +5896,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.02272049763405316</v>
+        <v>0.01742161239289812</v>
       </c>
       <c r="E238" t="n">
         <v>5</v>
@@ -5919,11 +5919,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.01846369865582104</v>
+        <v>0.01674464482420727</v>
       </c>
       <c r="E239" t="n">
         <v>6</v>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.01462519953521326</v>
+        <v>0.01269618470475322</v>
       </c>
       <c r="E240" t="n">
         <v>7</v>
@@ -5965,11 +5965,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.007995835481063219</v>
+        <v>0.006858682217839306</v>
       </c>
       <c r="E241" t="n">
         <v>8</v>
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.02371277463343708</v>
+        <v>0.02183006711368665</v>
       </c>
       <c r="E242" t="n">
         <v>1</v>
@@ -6011,11 +6011,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.02201481107602406</v>
+        <v>0.01970763579910777</v>
       </c>
       <c r="E243" t="n">
         <v>2</v>
@@ -6034,11 +6034,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.02130053703738404</v>
+        <v>0.01875853984968566</v>
       </c>
       <c r="E244" t="n">
         <v>3</v>
@@ -6057,11 +6057,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.0187482143810604</v>
+        <v>0.01835562636089545</v>
       </c>
       <c r="E245" t="n">
         <v>4</v>
@@ -6080,11 +6080,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>0.01827874555889996</v>
+        <v>0.01501388782500207</v>
       </c>
       <c r="E246" t="n">
         <v>5</v>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0.01621482944833388</v>
+        <v>0.01478082881698929</v>
       </c>
       <c r="E247" t="n">
         <v>6</v>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>0.01478140670953496</v>
+        <v>0.01201459591818521</v>
       </c>
       <c r="E248" t="n">
         <v>7</v>
@@ -6149,11 +6149,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0.003621493644139621</v>
+        <v>0.005322450969906582</v>
       </c>
       <c r="E249" t="n">
         <v>8</v>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0.04493073745636021</v>
+        <v>0.03150951223570677</v>
       </c>
       <c r="E250" t="n">
         <v>1</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0.02969690523628508</v>
+        <v>0.02709770601141503</v>
       </c>
       <c r="E251" t="n">
         <v>2</v>
@@ -6218,11 +6218,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0.02826513623329891</v>
+        <v>0.0252105223576436</v>
       </c>
       <c r="E252" t="n">
         <v>3</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0.02181235239294434</v>
+        <v>0.02176806902249691</v>
       </c>
       <c r="E253" t="n">
         <v>4</v>
@@ -6264,11 +6264,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0.02037548117575939</v>
+        <v>0.02039577584463573</v>
       </c>
       <c r="E254" t="n">
         <v>5</v>
@@ -6287,11 +6287,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0.01972006987322703</v>
+        <v>0.01771063648678751</v>
       </c>
       <c r="E255" t="n">
         <v>6</v>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0.01750339945220149</v>
+        <v>0.0163872455108202</v>
       </c>
       <c r="E256" t="n">
         <v>7</v>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0.01128354107755338</v>
+        <v>0.01093721374440794</v>
       </c>
       <c r="E257" t="n">
         <v>8</v>
@@ -6356,11 +6356,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0.05113542234606927</v>
+        <v>0.04671541749956636</v>
       </c>
       <c r="E258" t="n">
         <v>1</v>
@@ -6379,11 +6379,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.0335161124340828</v>
+        <v>0.03433213528761727</v>
       </c>
       <c r="E259" t="n">
         <v>2</v>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0.02811589193840828</v>
+        <v>0.03252824555586185</v>
       </c>
       <c r="E260" t="n">
         <v>3</v>
@@ -6425,11 +6425,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0.02663958380584974</v>
+        <v>0.03159384464524623</v>
       </c>
       <c r="E261" t="n">
         <v>4</v>
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0.02200908219982382</v>
+        <v>0.03125498839712389</v>
       </c>
       <c r="E262" t="n">
         <v>5</v>
@@ -6471,11 +6471,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.02094621210987152</v>
+        <v>0.02868687788817599</v>
       </c>
       <c r="E263" t="n">
         <v>6</v>
@@ -6494,11 +6494,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0.02034254692693653</v>
+        <v>0.0192430747845284</v>
       </c>
       <c r="E264" t="n">
         <v>7</v>
@@ -6517,11 +6517,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0.01034688236144578</v>
+        <v>0.01016679177852407</v>
       </c>
       <c r="E265" t="n">
         <v>8</v>
@@ -6540,11 +6540,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.0532851628336115</v>
+        <v>0.04482279937278525</v>
       </c>
       <c r="E266" t="n">
         <v>1</v>
@@ -6563,11 +6563,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.03389829938014778</v>
+        <v>0.0439534757124256</v>
       </c>
       <c r="E267" t="n">
         <v>2</v>
@@ -6586,11 +6586,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.03004216317036358</v>
+        <v>0.04185646305128417</v>
       </c>
       <c r="E268" t="n">
         <v>3</v>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0.02781778051291408</v>
+        <v>0.03364708139035174</v>
       </c>
       <c r="E269" t="n">
         <v>4</v>
@@ -6632,11 +6632,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.02397302499221051</v>
+        <v>0.02509690343776921</v>
       </c>
       <c r="E270" t="n">
         <v>5</v>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0.02244156181464551</v>
+        <v>0.0241328125178518</v>
       </c>
       <c r="E271" t="n">
         <v>6</v>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.0151745274823416</v>
+        <v>0.02141560291820015</v>
       </c>
       <c r="E272" t="n">
         <v>7</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.004859832501957309</v>
+        <v>0.005425954751908464</v>
       </c>
       <c r="E273" t="n">
         <v>8</v>
@@ -6724,11 +6724,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>0.0307658410250342</v>
+        <v>0.0258639928405956</v>
       </c>
       <c r="E274" t="n">
         <v>1</v>
@@ -6747,11 +6747,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0.02660330580870969</v>
+        <v>0.02051712911949881</v>
       </c>
       <c r="E275" t="n">
         <v>2</v>
@@ -6770,11 +6770,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>0.02656612513441884</v>
+        <v>0.01890770417437785</v>
       </c>
       <c r="E276" t="n">
         <v>3</v>
@@ -6793,11 +6793,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0.0240283048804926</v>
+        <v>0.01882147758558898</v>
       </c>
       <c r="E277" t="n">
         <v>4</v>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0.02308044741535821</v>
+        <v>0.01860571599246601</v>
       </c>
       <c r="E278" t="n">
         <v>5</v>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0.02127041860501845</v>
+        <v>0.01833910633257146</v>
       </c>
       <c r="E279" t="n">
         <v>6</v>
@@ -6862,11 +6862,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0.01832077623939331</v>
+        <v>0.01627197613887325</v>
       </c>
       <c r="E280" t="n">
         <v>7</v>
@@ -6885,11 +6885,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>0.004852466505548254</v>
+        <v>0.004883454937716367</v>
       </c>
       <c r="E281" t="n">
         <v>8</v>
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>0.03249707758068944</v>
+        <v>0.04985584668767024</v>
       </c>
       <c r="E282" t="n">
         <v>1</v>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>0.03152753473273977</v>
+        <v>0.03591864606334891</v>
       </c>
       <c r="E283" t="n">
         <v>2</v>
@@ -6954,11 +6954,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>0.03092555374662104</v>
+        <v>0.03352092894652124</v>
       </c>
       <c r="E284" t="n">
         <v>3</v>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>0.03091093987292269</v>
+        <v>0.03010895540194432</v>
       </c>
       <c r="E285" t="n">
         <v>4</v>
@@ -7000,11 +7000,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0.0298437736105913</v>
+        <v>0.02762235044219781</v>
       </c>
       <c r="E286" t="n">
         <v>5</v>
@@ -7023,11 +7023,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.02349523923801245</v>
+        <v>0.027370600259581</v>
       </c>
       <c r="E287" t="n">
         <v>6</v>
@@ -7046,11 +7046,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.0183327638912801</v>
+        <v>0.02696090134140119</v>
       </c>
       <c r="E288" t="n">
         <v>7</v>
@@ -7069,11 +7069,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.01576860229496305</v>
+        <v>0.008297041498081175</v>
       </c>
       <c r="E289" t="n">
         <v>8</v>
@@ -7092,11 +7092,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0.05132729692284529</v>
+        <v>0.03155657743988236</v>
       </c>
       <c r="E290" t="n">
         <v>1</v>
@@ -7115,11 +7115,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.03925642497415474</v>
+        <v>0.03074234901374682</v>
       </c>
       <c r="E291" t="n">
         <v>2</v>
@@ -7138,11 +7138,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.03297269707530181</v>
+        <v>0.02817676158313689</v>
       </c>
       <c r="E292" t="n">
         <v>3</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.02571268668442072</v>
+        <v>0.02403076965297136</v>
       </c>
       <c r="E293" t="n">
         <v>4</v>
@@ -7184,11 +7184,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.0236125975274854</v>
+        <v>0.02210032025518973</v>
       </c>
       <c r="E294" t="n">
         <v>5</v>
@@ -7207,11 +7207,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.02061324443451417</v>
+        <v>0.02061066857333321</v>
       </c>
       <c r="E295" t="n">
         <v>6</v>
@@ -7230,11 +7230,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.01587371718219997</v>
+        <v>0.01578892768147286</v>
       </c>
       <c r="E296" t="n">
         <v>7</v>
@@ -7253,11 +7253,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.006662525123605376</v>
+        <v>0.01417414565267901</v>
       </c>
       <c r="E297" t="n">
         <v>8</v>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.04928554520545893</v>
+        <v>0.04136453319739312</v>
       </c>
       <c r="E298" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.03731637753335371</v>
+        <v>0.03506259143613293</v>
       </c>
       <c r="E299" t="n">
         <v>2</v>
@@ -7322,11 +7322,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.03352992139361213</v>
+        <v>0.03160663046754628</v>
       </c>
       <c r="E300" t="n">
         <v>3</v>
@@ -7345,11 +7345,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.0311801988036336</v>
+        <v>0.02858545592047533</v>
       </c>
       <c r="E301" t="n">
         <v>4</v>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.02596836123136077</v>
+        <v>0.02837764470700803</v>
       </c>
       <c r="E302" t="n">
         <v>5</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.02591646196175118</v>
+        <v>0.02805980615845043</v>
       </c>
       <c r="E303" t="n">
         <v>6</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.02029665783180764</v>
+        <v>0.02596782227698497</v>
       </c>
       <c r="E304" t="n">
         <v>7</v>
@@ -7437,11 +7437,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.01490520758354032</v>
+        <v>0.01029238347693143</v>
       </c>
       <c r="E305" t="n">
         <v>8</v>
@@ -7460,11 +7460,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.0467966667694255</v>
+        <v>0.04180842022227619</v>
       </c>
       <c r="E306" t="n">
         <v>1</v>
@@ -7483,11 +7483,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>0.04586741908697923</v>
+        <v>0.03781488687363555</v>
       </c>
       <c r="E307" t="n">
         <v>2</v>
@@ -7506,11 +7506,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.03127558505846573</v>
+        <v>0.02864141477502044</v>
       </c>
       <c r="E308" t="n">
         <v>3</v>
@@ -7529,11 +7529,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.03072363175278397</v>
+        <v>0.02530737782623236</v>
       </c>
       <c r="E309" t="n">
         <v>4</v>
@@ -7552,11 +7552,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0.02922421958178708</v>
+        <v>0.02483669057168129</v>
       </c>
       <c r="E310" t="n">
         <v>5</v>
@@ -7575,11 +7575,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.02180564437453232</v>
+        <v>0.02048038240823582</v>
       </c>
       <c r="E311" t="n">
         <v>6</v>
@@ -7598,11 +7598,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0.01896643795464441</v>
+        <v>0.01468556908666971</v>
       </c>
       <c r="E312" t="n">
         <v>7</v>
@@ -7621,11 +7621,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.01750302850669764</v>
+        <v>0.009374378299568055</v>
       </c>
       <c r="E313" t="n">
         <v>8</v>
@@ -7644,11 +7644,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.07812896262476739</v>
+        <v>0.04557040654893607</v>
       </c>
       <c r="E314" t="n">
         <v>1</v>
@@ -7667,11 +7667,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.04256340213363032</v>
+        <v>0.04069459434213179</v>
       </c>
       <c r="E315" t="n">
         <v>2</v>
@@ -7690,11 +7690,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0.04118327545787505</v>
+        <v>0.04046633834290972</v>
       </c>
       <c r="E316" t="n">
         <v>3</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0.03108742228481216</v>
+        <v>0.03863732639396648</v>
       </c>
       <c r="E317" t="n">
         <v>4</v>
@@ -7736,11 +7736,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0.02806316185185758</v>
+        <v>0.02574752048434749</v>
       </c>
       <c r="E318" t="n">
         <v>5</v>
@@ -7759,11 +7759,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.02545896583691664</v>
+        <v>0.02192805482534723</v>
       </c>
       <c r="E319" t="n">
         <v>6</v>
@@ -7782,11 +7782,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0.01865346787877829</v>
+        <v>0.01632702820187032</v>
       </c>
       <c r="E320" t="n">
         <v>7</v>
@@ -7805,11 +7805,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.007370708897946043</v>
+        <v>0.005649857842939713</v>
       </c>
       <c r="E321" t="n">
         <v>8</v>
@@ -7828,11 +7828,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0.04343956370071127</v>
+        <v>0.03794284672896697</v>
       </c>
       <c r="E322" t="n">
         <v>1</v>
@@ -7851,11 +7851,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_device</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.03335907114638016</v>
+        <v>0.03305502950091338</v>
       </c>
       <c r="E323" t="n">
         <v>2</v>
@@ -7874,11 +7874,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>primary_device</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.02866462575270191</v>
+        <v>0.02514752429580654</v>
       </c>
       <c r="E324" t="n">
         <v>3</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>0.02388590084903502</v>
+        <v>0.02488852824741455</v>
       </c>
       <c r="E325" t="n">
         <v>4</v>
@@ -7920,11 +7920,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.02134365809601487</v>
+        <v>0.02466216978903647</v>
       </c>
       <c r="E326" t="n">
         <v>5</v>
@@ -7943,11 +7943,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0.01833159035683275</v>
+        <v>0.0223910649288573</v>
       </c>
       <c r="E327" t="n">
         <v>6</v>
@@ -7966,11 +7966,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.01696640526096677</v>
+        <v>0.02117282103758111</v>
       </c>
       <c r="E328" t="n">
         <v>7</v>
@@ -7989,11 +7989,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.01564775150897687</v>
+        <v>0.007023287093382425</v>
       </c>
       <c r="E329" t="n">
         <v>8</v>
